--- a/JsonConverter/ExcelFiles/EnemySpawnTable.xlsx
+++ b/JsonConverter/ExcelFiles/EnemySpawnTable.xlsx
@@ -24,16 +24,46 @@
     <x:t>Stage_001</x:t>
   </x:si>
   <x:si>
+    <x:t>스폰 시작 대기 시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생성할 유닛 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 규칙 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Enemy_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>StartDelay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최초 풀 생성 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 동시 생존 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TotalSpawnCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpawnInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EnemySpawn_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxAliveCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>InitialPoolSize</x:t>
   </x:si>
   <x:si>
     <x:t>ID</x:t>
   </x:si>
   <x:si>
-    <x:t>TotalSpawnCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생성할 유닛 ID</x:t>
+    <x:t>int</x:t>
   </x:si>
   <x:si>
     <x:t>스테이지 ID</x:t>
@@ -42,49 +72,19 @@
     <x:t>전체 생성 수</x:t>
   </x:si>
   <x:si>
+    <x:t>UnitID</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 생성 간격</x:t>
   </x:si>
   <x:si>
     <x:t>float</x:t>
   </x:si>
   <x:si>
-    <x:t>SpawnInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>InitialPoolSize</x:t>
-  </x:si>
-  <x:si>
     <x:t>StageID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UnitID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 시작 대기 시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 생성 간격</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 규칙 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Enemy_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최초 풀 생성 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 동시 생존 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxAliveCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EnemySpawn_001</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -127,26 +127,11 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="맑은 고딕"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff008000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="맑은 고딕"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff008000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff008000"/>
+    </x:font>
   </x:fonts>
   <x:fills count="8">
     <x:fill>
@@ -903,106 +888,106 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="2" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A4" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="12" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="12" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="1">
-        <x:v>3.5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="5">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G4" s="1">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3" ht="15.75" customHeight="1">
@@ -1016,9 +1001,9 @@
       <x:c r="C6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A7" s="4"/>
-      <x:c r="B7" s="4"/>
-      <x:c r="C7" s="4"/>
+      <x:c r="A7" s="6"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
     </x:row>
     <x:row r="8" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A8" s="7"/>
